--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T07:57:57+00:00</t>
+    <t>2024-04-23T09:09:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,19 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Example rule-based mappings between SNOMED CT to ICD-10-CM for fracture of ulna</t>
+    <t xml:space="preserve">Association </t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>Show example rule based mappings</t>
-  </si>
-  <si>
     <t>Copyright</t>
-  </si>
-  <si>
-    <t>Creative Commons 0</t>
   </si>
   <si>
     <t>Source</t>
@@ -367,17 +361,13 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -391,57 +381,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>30</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>33</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
     </row>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T09:09:38+00:00</t>
+    <t>2024-04-23T11:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,345 @@
   </si>
   <si>
     <t>urn:asip:ci-sis:cse-cs9:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.5.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cse-cs24:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.5.4</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:cse-mde:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.8</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:frcp:2011</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.9</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:idap:2011</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.10</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cva:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.1</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sap:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.2</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-snm:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sne:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.4</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-scm:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.5</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sem:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.13</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vsm:2012</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.15</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:aunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.16</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:eunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.17</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:sunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.18</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:crrtn:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.1</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:avk:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.2</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:tap:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dci:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.4</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:psc:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.5</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ppv:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.20</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pps-paerpa:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.21</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ldl-ees:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.22</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu:2015</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.23</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fludt:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.24</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fludr:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.25</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pavc:2016</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.26</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pps-cancer:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.27</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:d2lm-fin:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.28</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:d2lm-fidd:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.29</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ldl-ses:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.30</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:sdm-mr:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.32</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:crgm:2018</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.36</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:hr:2019</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.37</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vac:2019</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.38</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:tlm-da:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.39</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:pre:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.40</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-anest:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.41</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-cpa:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.42</t>
+  </si>
+  <si>
+    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.43</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.44</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.45</t>
+  </si>
+  <si>
+    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.46</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vac-note:2021</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.47</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:img-da:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.48</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.49</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.50</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.51</t>
+  </si>
+  <si>
+    <t>urn:ihe:pcc:ips:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.52</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:bio-ep-bio:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.54</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.55</t>
+  </si>
+  <si>
+    <t>urn:ihe:lab:xd-lab:2008</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.56</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ppp:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.57</t>
+  </si>
+  <si>
+    <t>urn:ihe:palm:apsr:2016</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.58</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.3.3</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.2.20</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:pdf:2008</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:text:2008</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:rtf:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:tiff:2010</t>
   </si>
 </sst>
 </file>
@@ -376,7 +715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -435,6 +774,666 @@
       </c>
       <c r="E4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T12:02:00+00:00</t>
+    <t>2024-04-23T12:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDANonStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure</t>
   </si>
   <si>
     <t/>
@@ -121,6 +121,345 @@
   </si>
   <si>
     <t>urn:asip:ci-sis:cse-cs9:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.5.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cse-cs24:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.5.4</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:cse-mde:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.8</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:frcp:2011</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.9</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:idap:2011</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.10</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cva:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.1</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sap:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.2</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-snm:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sne:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.4</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-scm:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.12.5</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:obp-sem:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.13</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vsm:2012</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.15</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:aunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.16</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:eunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.17</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:sunv:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.18</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:crrtn:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.1</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:avk:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.2</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:tap:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.3</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dci:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.4</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:psc:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.2.1.5</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ppv:2009</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.20</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pps-paerpa:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.21</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ldl-ees:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.22</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu:2015</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.23</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fludt:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.24</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fludr:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.25</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pavc:2016</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.26</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:pps-cancer:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.27</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:d2lm-fin:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.28</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:d2lm-fidd:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.29</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ldl-ses:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.30</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:sdm-mr:2017</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.32</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:crgm:2018</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.36</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:hr:2019</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.37</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vac:2019</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.38</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:tlm-da:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.39</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:pre:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.40</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-anest:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.41</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-cpa:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.42</t>
+  </si>
+  <si>
+    <t>urn:ihe:eyecare:geneyeevalcn:2014</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.43</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.44</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.45</t>
+  </si>
+  <si>
+    <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.46</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vac-note:2021</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.47</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:img-da:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.48</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.49</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.50</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.51</t>
+  </si>
+  <si>
+    <t>urn:ihe:pcc:ips:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.52</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:bio-ep-bio:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.54</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.55</t>
+  </si>
+  <si>
+    <t>urn:ihe:lab:xd-lab:2008</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.56</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ppp:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.57</t>
+  </si>
+  <si>
+    <t>urn:ihe:palm:apsr:2016</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.58</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.3.3</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.2.20</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:pdf:2008</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti:xds-sd:text:2008</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:jpeg:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:rtf:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:iti-fr:xds-sd:tiff:2010</t>
   </si>
 </sst>
 </file>
@@ -376,7 +715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -435,6 +774,666 @@
       </c>
       <c r="E4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
+    <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="150">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T12:54:40+00:00</t>
+    <t>2024-04-23T13:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,6 +440,9 @@
   </si>
   <si>
     <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDANonStructure</t>
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.3.3</t>
@@ -715,7 +719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1368,71 +1372,115 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T13:53:01+00:00</t>
+    <t>2024-04-24T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:17:51+00:00</t>
+    <t>2024-04-24T07:20:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t xml:space="preserve">CDA-&gt;templateID to XDS-&gt;formatCode </t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -58,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:20:21+00:00</t>
+    <t>2024-04-24T07:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Association </t>
+    <t>Lorsque le corps du CDA est structuré, la métadonnée 'formatCode' provient de l'élément 'templateId' (modèle du document structuré). La correspondance entre templateId et formatCode est assurée par cette table d'association</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -94,22 +97,28 @@
     <t>Source</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDAStructure</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+  </si>
+  <si>
     <t>Display</t>
   </si>
   <si>
     <t>Relationship</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R220-ModeleDocumentCDAStructure/FHIR/TRE-R220-ModeleDocumentCDAStructure</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A06-FormatCodeComplementaire/FHIR/TRE-A06-FormatCodeComplementaire</t>
   </si>
   <si>
     <t>1.2.250.1.213.1.1.1.5.1</t>
@@ -442,7 +451,7 @@
     <t>urn:asip:ci-sis:export-dui:2023</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDANonStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.3.3</t>
@@ -597,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -641,76 +650,92 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -724,651 +749,651 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1384,101 +1409,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E8" s="2"/>
     </row>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -43,9 +43,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t xml:space="preserve">CDA-&gt;templateID to XDS-&gt;formatCode </t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -61,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:47:38+00:00</t>
+    <t>2024-04-25T08:18:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,7 +94,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDAStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDA</t>
   </si>
   <si>
     <t>Target</t>
@@ -451,10 +448,13 @@
     <t>urn:asip:ci-sis:export-dui:2023</t>
   </si>
   <si>
+    <t>1.3.6.1.4.1.19376.1.3.3</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R221-ModeleDocumentCDANonStructure/FHIR/TRE-R221-ModeleDocumentCDANonStructure</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
-  </si>
-  <si>
-    <t>1.3.6.1.4.1.19376.1.3.3</t>
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.2.20</t>
@@ -650,91 +650,91 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -744,658 +744,669 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>31</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E59" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1404,51 +1415,51 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>31</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>33</v>
-      </c>
       <c r="C2" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1459,7 +1470,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1470,7 +1481,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1481,7 +1492,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1492,20 +1503,9 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:18:53+00:00</t>
+    <t>2024-04-25T11:48:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,9 @@
     <t>1.2.250.1.213.1.1.1.5.1</t>
   </si>
   <si>
+    <t>equivalent</t>
+  </si>
+  <si>
     <t>urn:asip:ci-sis:cse-cs8:2017</t>
   </si>
   <si>
@@ -458,6 +461,9 @@
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.2.20</t>
+  </si>
+  <si>
+    <t>source-is-broader-than-target</t>
   </si>
   <si>
     <t>urn:ihe:iti:xds-sd:pdf:2008</t>
@@ -786,625 +792,739 @@
         <v>34</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="C31" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="C32" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="C33" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D33" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D39" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+      <c r="C41" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="C42" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D43" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="C48" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D50" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="C51" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D51" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="C52" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D52" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="C53" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D53" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="C54" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="C56" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D56" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="C57" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D58" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="C59" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="D59" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1437,7 +1557,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>32</v>
@@ -1446,7 +1566,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -1454,56 +1574,66 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D3" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D4" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D5" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D6" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7" s="2"/>
     </row>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:48:40+00:00</t>
+    <t>2024-04-25T14:16:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,10 +455,10 @@
     <t>1.3.6.1.4.1.19376.1.3.3</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R221-ModeleDocumentCDANonStructure/FHIR/TRE-R221-ModeleDocumentCDANonStructure</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
   </si>
   <si>
     <t>1.3.6.1.4.1.19376.1.2.20</t>
@@ -1535,6 +1536,167 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -1557,7 +1719,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>32</v>
@@ -1566,7 +1728,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>

--- a/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS_A11-CorresModeleCDA-XdsFormatCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T14:16:56+00:00</t>
+    <t>2024-05-02T08:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,22 +344,85 @@
     <t>urn:asip:ci-sis:tlm-da:2020</t>
   </si>
   <si>
+    <t>1.2.250.1.213.1.1.1.40</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-anest:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.41</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:cr-cpa:2020</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.46</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:vac-note:2021</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.47</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:img-da:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.48</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.49</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.50</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.52</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:bio-ep-bio:2022</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.56</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ppp:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.57</t>
+  </si>
+  <si>
+    <t>urn:ihe:palm:apsr:2016</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
+  </si>
+  <si>
     <t>1.2.250.1.213.1.1.1.39</t>
   </si>
   <si>
     <t>urn:ihe:pharm:pre:2010</t>
   </si>
   <si>
-    <t>1.2.250.1.213.1.1.1.40</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:cr-anest:2020</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.41</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:cr-cpa:2020</t>
+    <t>1.2.250.1.213.1.1.1.58</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.54</t>
+  </si>
+  <si>
+    <t>urn:ihe:pharm:dis:2010</t>
   </si>
   <si>
     <t>1.2.250.1.213.1.1.1.42</t>
@@ -380,82 +443,19 @@
     <t>urn:ihe:rad:CDA:ImagingReportStructuredHeadings:2013</t>
   </si>
   <si>
-    <t>1.2.250.1.213.1.1.1.46</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:vac-note:2021</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.47</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:img-da:2022</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.48</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.49</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.50</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
+    <t>1.2.250.1.213.1.1.1.55</t>
+  </si>
+  <si>
+    <t>urn:ihe:lab:xd-lab:2008</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.3.3</t>
   </si>
   <si>
     <t>1.2.250.1.213.1.1.1.51</t>
   </si>
   <si>
     <t>urn:ihe:pcc:ips:2020</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.52</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:bio-ep-bio:2022</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.54</t>
-  </si>
-  <si>
-    <t>urn:ihe:pharm:dis:2010</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.55</t>
-  </si>
-  <si>
-    <t>urn:ihe:lab:xd-lab:2008</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.56</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:ppp:2023</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.57</t>
-  </si>
-  <si>
-    <t>urn:ihe:palm:apsr:2016</t>
-  </si>
-  <si>
-    <t>1.2.250.1.213.1.1.1.58</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:export-dui:2023</t>
-  </si>
-  <si>
-    <t>1.3.6.1.4.1.19376.1.3.3</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R221-ModeleDocumentCDANonStructure/FHIR/TRE-R221-ModeleDocumentCDANonStructure</t>
@@ -751,7 +751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1330,204 +1330,74 @@
         <v>35</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B55" s="2"/>
-      <c r="C55" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B56" s="2"/>
-      <c r="C56" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D56" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B57" s="2"/>
-      <c r="C57" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B58" s="2"/>
-      <c r="C58" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D58" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E59" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1536,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1567,7 +1437,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
@@ -1575,120 +1445,159 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1728,7 +1637,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
